--- a/planning/로스팅_필요량.xlsx
+++ b/planning/로스팅_필요량.xlsx
@@ -451,7 +451,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>카페쇼 시음용 로스팅 필요량 (11/3~7, 2026-10-28 시안)</t>
+          <t>카페쇼 시음용 로스팅 필요량 (11/3~7, 2026-10-28 수정: 발표 3분·블랙 에스프레소)</t>
         </is>
       </c>
     </row>
@@ -469,11 +469,11 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>900</v>
+        <v>1350</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>처리량_계산.xlsx 최대값</t>
+          <t>처리량_계산.xlsx 4일 합계(발표 3분+교대 1분 기준) — 그 표가 바뀌면 여기도 고치기</t>
         </is>
       </c>
     </row>
@@ -510,37 +510,37 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>블랙 추출 비율(원두 g : 물 ml) 물</t>
+          <t>블랙 1잔 원두(g) — 에스프레소 1샷 도징</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>추정: 1:15 드립 기준. 추출 방식 정해지면 고치기</t>
+          <t>추정: 대표 레시피로 고치기. 블랙 3종은 에스프레소 머신 1그룹 추출(대표 10/28)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>원두가 머금는 물(원두 g당 ml)</t>
+          <t>블랙 1잔 양(ml) — 샷 + 물(아메리카노)</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>2</v>
+        <v>240</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>추정</t>
+          <t>추정: 대표 레시피로 고치기</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>라떼 1통 원두(g)</t>
+          <t>라떼 1배합 원두(g)</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -548,14 +548,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>결정사항 10/6: 에스프레소 20g 도징</t>
+          <t>결정사항 10/6: 1배합 = 에스프레소 1샷(20g 도징→41g) + 우유 280g. 통은 이 배합 ×20(약 6.4L)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>라떼 1통 양(ml) = 에스프레소 41 + 우유 280</t>
+          <t>라떼 1배합 양(ml) = 에스프레소 41 + 우유 280</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -570,7 +570,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>라떼 1통 우유(ml)</t>
+          <t>라떼 1배합 우유(ml)</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -604,11 +604,11 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>추정: 홀빈 밥그릇 + 매일 아침 분쇄 반찬그릇 4일</t>
+          <t>대표 10/28: 진열 샘플은 로스팅 뒤 모아 둔 결점두를 씀 → 새로 볶지 않음</t>
         </is>
       </c>
     </row>
@@ -714,7 +714,7 @@
         <v/>
       </c>
       <c r="E19" s="4">
-        <f>1/($B$7-$B$8)</f>
+        <f>$B$7/$B$8</f>
         <v/>
       </c>
       <c r="F19" s="4">
@@ -741,7 +741,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>허벌 블렌드</t>
+          <t>허벌 블랜드</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -758,7 +758,7 @@
         <v/>
       </c>
       <c r="E20" s="4">
-        <f>1/($B$7-$B$8)</f>
+        <f>$B$7/$B$8</f>
         <v/>
       </c>
       <c r="F20" s="4">
@@ -846,7 +846,7 @@
         <v/>
       </c>
       <c r="E22" s="4">
-        <f>1/($B$7-$B$8)</f>
+        <f>$B$7/$B$8</f>
         <v/>
       </c>
       <c r="F22" s="4">
@@ -905,7 +905,6 @@
         <v/>
       </c>
     </row>
-    <row r="24"/>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
@@ -935,7 +934,6 @@
         <v/>
       </c>
     </row>
-    <row r="28"/>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
